--- a/Web/TestCasesWeb/CopiasSeguridad_backups.xlsx
+++ b/Web/TestCasesWeb/CopiasSeguridad_backups.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52C3E3C-5892-494F-8A41-C5989B168990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8DE2DC-AD3B-454E-8558-6A448A6022EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="39">
   <si>
     <t>Num</t>
   </si>
@@ -46,24 +46,12 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>The Backup's page home</t>
-  </si>
-  <si>
     <t>BACKUP001</t>
   </si>
   <si>
-    <t>1. The backup page home is correctly.</t>
-  </si>
-  <si>
-    <t>1. The user clicks "Backup"</t>
-  </si>
-  <si>
     <t>KO</t>
   </si>
   <si>
-    <t>Cambiar nombre "Backup" por "Copia de seguridad"</t>
-  </si>
-  <si>
     <t>BACKUP002</t>
   </si>
   <si>
@@ -73,12 +61,6 @@
     <t>BACKUP004</t>
   </si>
   <si>
-    <t>Create backup</t>
-  </si>
-  <si>
-    <t>Delete backup</t>
-  </si>
-  <si>
     <t>1. The backup is created.</t>
   </si>
   <si>
@@ -88,19 +70,10 @@
     <t>1. The user clicks "Crear respaldo completo"</t>
   </si>
   <si>
-    <t>1. The user selects a backup.</t>
-  </si>
-  <si>
     <t>BACKUP005</t>
   </si>
   <si>
     <t>OK</t>
-  </si>
-  <si>
-    <t>1. The backup page home is not correctly.</t>
-  </si>
-  <si>
-    <t>Create backup: Change restaurant</t>
   </si>
   <si>
     <t xml:space="preserve">1. The user selects a different restaurant.
@@ -108,21 +81,74 @@
 </t>
   </si>
   <si>
-    <t>Delete backup: Download</t>
-  </si>
-  <si>
     <t>1. The user selects a backup.
 2. Clicks icon "download"</t>
   </si>
   <si>
     <t>1. The backup is downloaded</t>
+  </si>
+  <si>
+    <t>The Backup's page</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Backups"</t>
+  </si>
+  <si>
+    <t>1. The backup page is correctly.</t>
+  </si>
+  <si>
+    <t>Cambiar nombre "Backups" por "Copias de seguridad"</t>
+  </si>
+  <si>
+    <t>1. The user selects a backup
+2. Clicks "Confirmar eliminación"</t>
+  </si>
+  <si>
+    <t>1. The user selects a backup
+2. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The operation is canceled.</t>
+  </si>
+  <si>
+    <t>BACKUP006</t>
+  </si>
+  <si>
+    <t>Backup: create</t>
+  </si>
+  <si>
+    <t>Backup: delete</t>
+  </si>
+  <si>
+    <t>Backup: delete, cancel</t>
+  </si>
+  <si>
+    <t>Backup: Change restaurant</t>
+  </si>
+  <si>
+    <t>Backup: Download</t>
+  </si>
+  <si>
+    <t>Backup: Synchronization</t>
+  </si>
+  <si>
+    <t>1. The user sees the backup created by web in app</t>
+  </si>
+  <si>
+    <t>1. Backup synchronization is performed</t>
+  </si>
+  <si>
+    <t>Las copias de seguridad creadas en el backoffice no se ven en el POS: COPSEG002.jpg</t>
+  </si>
+  <si>
+    <t>BACKUP007</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,6 +178,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -193,7 +226,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -215,6 +248,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -556,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -592,30 +628,28 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>12</v>
-      </c>
       <c r="H2" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -623,100 +657,148 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>17</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="4"/>
+      <c r="C7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G6">
+  <conditionalFormatting sqref="G2:G8">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>

--- a/Web/TestCasesWeb/CopiasSeguridad_backups.xlsx
+++ b/Web/TestCasesWeb/CopiasSeguridad_backups.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8DE2DC-AD3B-454E-8558-6A448A6022EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{748B6EF6-F016-4D44-AED3-A66C80B4A55D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="43">
   <si>
     <t>Num</t>
   </si>
@@ -129,9 +129,6 @@
     <t>Backup: Download</t>
   </si>
   <si>
-    <t>Backup: Synchronization</t>
-  </si>
-  <si>
     <t>1. The user sees the backup created by web in app</t>
   </si>
   <si>
@@ -142,6 +139,21 @@
   </si>
   <si>
     <t>BACKUP007</t>
+  </si>
+  <si>
+    <t>BACKUP008</t>
+  </si>
+  <si>
+    <t>Backup: Synchronization to POS</t>
+  </si>
+  <si>
+    <t>Backup: Synchronization from POS</t>
+  </si>
+  <si>
+    <t>Una copia creada en el POS no se ve en el backoffice.</t>
+  </si>
+  <si>
+    <t>1. The user sees the backup created by app in backoffice</t>
   </si>
 </sst>
 </file>
@@ -592,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -777,28 +789,52 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="7" t="s">
         <v>9</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G8">
+  <conditionalFormatting sqref="G2:G9">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
